--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-molekulare-pathogenlast-methode-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
